--- a/役割分担表.xlsx
+++ b/役割分担表.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HigutiHaruyuki\Documents\GitHub\Fugedaku_TeamKagoshima\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6411AB55-51F5-4360-9390-380B5D00292C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EB308B-046B-4267-B4A6-77E924AABE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$B$2:$I$34</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="61">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -55,6 +59,399 @@
   </si>
   <si>
     <t>リザルトシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>石田</t>
+    <rPh sb="0" eb="2">
+      <t>イシダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>野添</t>
+    <rPh sb="0" eb="2">
+      <t>ノゾエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>樋口</t>
+    <rPh sb="0" eb="2">
+      <t>ヒグチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山下</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマシタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>玉利</t>
+    <rPh sb="0" eb="2">
+      <t>タマリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI（メインシーン）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全員</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>概要</t>
+    <rPh sb="0" eb="2">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>優先度</t>
+    <rPh sb="0" eb="3">
+      <t>ユウセンド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バージョン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業工数</t>
+    <rPh sb="0" eb="4">
+      <t>サギョウコウスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実コスト</t>
+    <rPh sb="0" eb="1">
+      <t>ジツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進捗状況</t>
+    <rPh sb="0" eb="4">
+      <t>シンチョクジョウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテム取得処理</t>
+    <rPh sb="4" eb="8">
+      <t>シュトクショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁に反射する判定</t>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンシャ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動アニメーション</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプアニメーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>落下時のアニメーション</t>
+    <rPh sb="0" eb="2">
+      <t>ラッカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>足場の当たり判定</t>
+    <rPh sb="0" eb="2">
+      <t>アシバ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>足場の配置</t>
+    <rPh sb="0" eb="2">
+      <t>アシバ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラ移動</t>
+    <rPh sb="3" eb="5">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>滑る床</t>
+    <rPh sb="0" eb="1">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ユカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火山灰</t>
+    <rPh sb="0" eb="3">
+      <t>カザンバイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沼</t>
+    <rPh sb="0" eb="1">
+      <t>ヌマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ回数の保存</t>
+    <rPh sb="4" eb="6">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風アニメーション</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火山灰アニメーション</t>
+    <rPh sb="0" eb="3">
+      <t>カザンバイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沼見た目</t>
+    <rPh sb="0" eb="1">
+      <t>ヌマ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間表示</t>
+    <rPh sb="0" eb="4">
+      <t>ジカンヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムの状態表示</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズ画面関係</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロゴが動くアニメーション</t>
+    <rPh sb="3" eb="4">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIと配置</t>
+    <rPh sb="3" eb="5">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>落下回数の保存</t>
+    <rPh sb="0" eb="2">
+      <t>ラッカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ（溜める）</t>
+    <rPh sb="5" eb="6">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サウンド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>録音</t>
+    <rPh sb="0" eb="2">
+      <t>ロクオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>担当の理由</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>リユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>玉利と山下は</t>
+    <rPh sb="0" eb="2">
+      <t>タマリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヤマシタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>担当</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリアタイムとジャンプ回数、落下した回数をリザルトシーンに表示</t>
+    <rPh sb="14" eb="16">
+      <t>ラッカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン遷移</t>
+    <rPh sb="3" eb="5">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>素材集め</t>
+    <rPh sb="0" eb="3">
+      <t>ソザイアツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーモデル</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -62,7 +459,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,16 +474,72 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF81C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6969"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -94,18 +547,201 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF6969"/>
+      <color rgb="FFDF81C0"/>
+      <color rgb="FFFF99CC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -380,41 +1016,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
         <v>4</v>
       </c>
     </row>
@@ -422,4 +1079,747 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA18566-FC65-4B72-B44D-26E55DC84C88}">
+  <dimension ref="B1:M58"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="61.125" customWidth="1"/>
+    <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13.75" customWidth="1"/>
+    <col min="7" max="7" width="14.625" customWidth="1"/>
+    <col min="8" max="8" width="13.75" customWidth="1"/>
+    <col min="9" max="9" width="11.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B1" s="11"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B2" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="8"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+    </row>
+    <row r="3" spans="2:13">
+      <c r="B3" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" spans="2:13">
+      <c r="B4" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="30"/>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B14" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B15" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="B16" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" spans="2:12">
+      <c r="B18" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="B20" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+    </row>
+    <row r="21" spans="2:12">
+      <c r="B21" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+    </row>
+    <row r="22" spans="2:12">
+      <c r="B22" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+    </row>
+    <row r="23" spans="2:12">
+      <c r="B23" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+    </row>
+    <row r="24" spans="2:12">
+      <c r="B24" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+    </row>
+    <row r="25" spans="2:12">
+      <c r="B25" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+    </row>
+    <row r="26" spans="2:12">
+      <c r="B26" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+    </row>
+    <row r="27" spans="2:12">
+      <c r="B27" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+    </row>
+    <row r="28" spans="2:12">
+      <c r="B28" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+    </row>
+    <row r="29" spans="2:12">
+      <c r="B29" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="10"/>
+    </row>
+    <row r="30" spans="2:12">
+      <c r="B30" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="10"/>
+    </row>
+    <row r="31" spans="2:12">
+      <c r="B31" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="10"/>
+    </row>
+    <row r="32" spans="2:12">
+      <c r="B32" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="10"/>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="10"/>
+    </row>
+    <row r="34" spans="2:9" ht="19.5" thickBot="1">
+      <c r="B34" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="12"/>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="C35" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9">
+      <c r="D36" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4">
+      <c r="C58" t="s">
+        <v>50</v>
+      </c>
+      <c r="D58" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:I34" xr:uid="{FFA18566-FC65-4B72-B44D-26E55DC84C88}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:I2">
+    <sortCondition ref="C2"/>
+  </sortState>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/役割分担表.xlsx
+++ b/役割分担表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HigutiHaruyuki\Documents\GitHub\Fugedaku_TeamKagoshima\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a833777a10b1dd4/Documents/GitHub/Fugedaku_TeamKagoshima/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EB308B-046B-4267-B4A6-77E924AABE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="245" documentId="13_ncr:1_{93EB308B-046B-4267-B4A6-77E924AABE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46FC8097-C0C7-40F3-B51D-6A2619B81C18}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,19 +17,30 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$B$2:$I$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$B$2:$I$36</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="77">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -291,19 +302,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>沼見た目</t>
-    <rPh sb="0" eb="1">
-      <t>ヌマ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>時間表示</t>
     <rPh sb="0" eb="4">
       <t>ジカンヒョウジ</t>
@@ -394,16 +392,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>玉利と山下は</t>
-    <rPh sb="0" eb="2">
-      <t>タマリ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヤマシタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>担当</t>
     <rPh sb="0" eb="2">
       <t>タントウ</t>
@@ -411,16 +399,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>クリアタイムとジャンプ回数、落下した回数をリザルトシーンに表示</t>
-    <rPh sb="14" eb="16">
-      <t>ラッカ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>カイスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>シーン遷移</t>
     <rPh sb="3" eb="5">
       <t>センイ</t>
@@ -453,13 +431,116 @@
   <si>
     <t>プレイヤーモデル</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未着手</t>
+    <rPh sb="0" eb="3">
+      <t>ミチャクシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ選択シーン</t>
+    <rPh sb="4" eb="6">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン遷移とUI、ステージ選択script</t>
+    <rPh sb="3" eb="5">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1コスト1時間</t>
+    <rPh sb="5" eb="7">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間の保存</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>落下した回数をリザルトシーンに表示</t>
+  </si>
+  <si>
+    <t>クリアタイムとジャンプ回数の表示</t>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロト</t>
+  </si>
+  <si>
+    <t>プロト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベータ</t>
+  </si>
+  <si>
+    <t>ベータ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファ</t>
+  </si>
+  <si>
+    <t>アルファ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>玉利と山下は自宅にPCが現状ないため、部活内での作業となるため</t>
+    <rPh sb="6" eb="8">
+      <t>ジタク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>ブカツナイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>サギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予想コスト</t>
+  </si>
+  <si>
+    <t>残りコスト</t>
+  </si>
+  <si>
+    <t>実コスト</t>
+  </si>
+  <si>
+    <t>全体の作業時間</t>
+  </si>
+  <si>
+    <t>作業中(作業工数)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -482,8 +563,25 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -528,18 +626,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDF81C0"/>
+        <fgColor rgb="FFFF6969"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF6969"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -576,17 +722,6 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -621,17 +756,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -688,11 +812,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -701,34 +840,61 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -751,6 +917,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1083,739 +1253,995 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA18566-FC65-4B72-B44D-26E55DC84C88}">
-  <dimension ref="B1:M58"/>
+  <dimension ref="B1:O41"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="3" max="3" width="26.25" customWidth="1"/>
     <col min="4" max="4" width="61.125" customWidth="1"/>
     <col min="5" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
     <col min="7" max="7" width="14.625" customWidth="1"/>
     <col min="8" max="8" width="13.75" customWidth="1"/>
     <col min="9" max="9" width="11.875" customWidth="1"/>
+    <col min="12" max="12" width="22.125" customWidth="1"/>
+    <col min="13" max="13" width="13.625" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B1" s="11"/>
-      <c r="C1" s="6"/>
+    <row r="1" spans="2:15" ht="19.5" thickBot="1">
+      <c r="B1" s="8"/>
+      <c r="C1" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="F1" s="8"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="9"/>
-    </row>
-    <row r="2" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B2" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="13" t="s">
+    </row>
+    <row r="2" spans="2:15" ht="19.5" thickBot="1">
+      <c r="B2" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-    </row>
-    <row r="3" spans="2:13">
-      <c r="B3" s="25" t="s">
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="2:15">
+      <c r="B3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="24">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="B4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="26">
+        <v>1</v>
+      </c>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="B5" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="26">
+        <v>2</v>
+      </c>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="N5" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="O5" s="29" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15">
+      <c r="B6" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="26">
+        <v>1</v>
+      </c>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M6" s="29">
+        <f>SUM(G3:G38)</f>
+        <v>57</v>
+      </c>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+    </row>
+    <row r="7" spans="2:15">
+      <c r="B7" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="26">
+        <v>1</v>
+      </c>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="L7" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7" s="29">
+        <f>SUMIF(F3:F38,"プロト",G3:G38)</f>
+        <v>27</v>
+      </c>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="B8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="26">
+        <v>1</v>
+      </c>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" s="29">
+        <f>SUMIF(F3:F38,"アルファ",G3:G38)</f>
+        <v>18</v>
+      </c>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="B9" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="26">
+        <v>2</v>
+      </c>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" s="29">
+        <f>SUMIF(F3:F38,"ベータ",G3:G38)</f>
+        <v>12</v>
+      </c>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+    </row>
+    <row r="10" spans="2:15">
+      <c r="B10" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="26">
+        <v>2</v>
+      </c>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+    </row>
+    <row r="11" spans="2:15">
+      <c r="B11" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="26">
+        <v>1</v>
+      </c>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15">
+      <c r="B12" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="26">
+        <v>4</v>
+      </c>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="19"/>
+    </row>
+    <row r="13" spans="2:15">
+      <c r="B13" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="26">
+        <v>3</v>
+      </c>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" ht="19.5" thickBot="1">
+      <c r="B14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="26">
+        <v>3</v>
+      </c>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" ht="19.5" thickBot="1">
+      <c r="B15" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" spans="2:15">
+      <c r="B16" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="26">
+        <v>1</v>
+      </c>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="26">
+        <v>3</v>
+      </c>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="26">
+        <v>3</v>
+      </c>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" s="26">
+        <v>1</v>
+      </c>
+      <c r="H28" s="26"/>
+      <c r="I28" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29" s="26">
+        <v>2</v>
+      </c>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" s="26">
+        <v>2</v>
+      </c>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G32" s="26">
+        <v>2</v>
+      </c>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G33" s="26">
+        <v>1</v>
+      </c>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9">
+      <c r="B36" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G36" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="H36" s="26"/>
+      <c r="I36" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-    </row>
-    <row r="4" spans="2:13">
-      <c r="B4" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="15" t="s">
+      <c r="D37" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="15" t="s">
+      <c r="E37" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F37" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="G37" s="26">
+        <v>2</v>
+      </c>
+      <c r="H37" s="26"/>
+      <c r="I37" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" ht="19.5" thickBot="1">
+      <c r="B38" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-    </row>
-    <row r="6" spans="2:13">
-      <c r="B6" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-    </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="15" t="s">
+      <c r="D38" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-    </row>
-    <row r="10" spans="2:13">
-      <c r="B10" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-    </row>
-    <row r="12" spans="2:13">
-      <c r="B12" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="30"/>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="B13" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-    </row>
-    <row r="14" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B14" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-    </row>
-    <row r="15" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B15" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="15" t="s">
+      <c r="E38" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="G38" s="28">
         <v>2</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="13"/>
-    </row>
-    <row r="16" spans="2:13">
-      <c r="B16" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="2:12">
-      <c r="B17" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-    </row>
-    <row r="18" spans="2:12">
-      <c r="B18" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-    </row>
-    <row r="19" spans="2:12">
-      <c r="B19" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-    </row>
-    <row r="20" spans="2:12">
-      <c r="B20" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-    </row>
-    <row r="21" spans="2:12">
-      <c r="B21" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-    </row>
-    <row r="22" spans="2:12">
-      <c r="B22" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-    </row>
-    <row r="23" spans="2:12">
-      <c r="B23" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-    </row>
-    <row r="24" spans="2:12">
-      <c r="B24" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-    </row>
-    <row r="25" spans="2:12">
-      <c r="B25" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-    </row>
-    <row r="26" spans="2:12">
-      <c r="B26" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-    </row>
-    <row r="27" spans="2:12">
-      <c r="B27" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-    </row>
-    <row r="28" spans="2:12">
-      <c r="B28" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-    </row>
-    <row r="29" spans="2:12">
-      <c r="B29" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="10"/>
-    </row>
-    <row r="30" spans="2:12">
-      <c r="B30" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="10"/>
-    </row>
-    <row r="31" spans="2:12">
-      <c r="B31" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="10"/>
-    </row>
-    <row r="32" spans="2:12">
-      <c r="B32" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="10"/>
-    </row>
-    <row r="33" spans="2:9">
-      <c r="B33" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="10"/>
-    </row>
-    <row r="34" spans="2:9" ht="19.5" thickBot="1">
-      <c r="B34" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="27" t="s">
+      <c r="H38" s="28"/>
+      <c r="I38" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9">
+      <c r="I39" s="6"/>
+    </row>
+    <row r="41" spans="2:9">
+      <c r="C41" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="12"/>
-    </row>
-    <row r="35" spans="2:9">
-      <c r="C35" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9">
-      <c r="D36" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="58" spans="3:4">
-      <c r="C58" t="s">
-        <v>50</v>
-      </c>
-      <c r="D58" t="s">
-        <v>51</v>
+      <c r="D41" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:I34" xr:uid="{FFA18566-FC65-4B72-B44D-26E55DC84C88}"/>
+  <autoFilter ref="B2:I36" xr:uid="{FFA18566-FC65-4B72-B44D-26E55DC84C88}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:I2">
     <sortCondition ref="C2"/>
   </sortState>

--- a/役割分担表.xlsx
+++ b/役割分担表.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a833777a10b1dd4/Documents/GitHub/Fugedaku_TeamKagoshima/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NozoeYuki\Documents\GitHub\Fugedaku_TeamKagoshima\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="13_ncr:1_{93EB308B-046B-4267-B4A6-77E924AABE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46FC8097-C0C7-40F3-B51D-6A2619B81C18}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB943968-0C56-4CF7-A336-503A12713916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="コスト表" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$B$2:$I$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">コスト表!$B$2:$I$36</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -917,10 +917,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1188,6 +1184,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
